--- a/maestros/Intervenciones_P2R_Ondupack.xlsx
+++ b/maestros/Intervenciones_P2R_Ondupack.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">P2R-01 · Gestión de la demanda</t>
   </si>
   <si>
-    <t xml:space="preserve">HT-P2R-13</t>
+    <t xml:space="preserve">HT-P2R-01</t>
   </si>
   <si>
     <t xml:space="preserve">Negocio</t>
